--- a/Train_A_Skill/Level1_Skill_Vertical_BentArmPull_ChinUpPullUp.xlsx
+++ b/Train_A_Skill/Level1_Skill_Vertical_BentArmPull_ChinUpPullUp.xlsx
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -172,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1334,9 +1337,9 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>○  4</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1356,9 +1359,9 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>○  4</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1627,44 +1630,44 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>TEST: Ring/ Bar Chinup</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PASS: 5 reps</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>1–5 reps · 2 sets  ✦</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>TEST: Ring/ Bar Pullups</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>PASS: 5 reps</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>1–5 reps · 2 sets  ✦</t>
         </is>
